--- a/03_Outputs/San_Juan/09_Salud/salud.xlsx
+++ b/03_Outputs/San_Juan/09_Salud/salud.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>0.0852713178294573</v>
+        <v>0.0852713178294574</v>
       </c>
     </row>
     <row r="7">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.0852713178294573</v>
+        <v>0.0852713178294574</v>
       </c>
     </row>
     <row r="7">
